--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29912"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4EE0F0-3C19-944D-83B8-607E51890B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89BA6C22-350D-4EED-92D2-764B3F470D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="25340" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="161">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -122,10 +122,59 @@
     <t>Student 1:</t>
   </si>
   <si>
+    <t>George Dan-Cristian</t>
+  </si>
+  <si>
     <t>Student 2:</t>
   </si>
   <si>
+    <t>Grava Bianca-Adelina</t>
+  </si>
+  <si>
     <t>Student 3:</t>
+  </si>
+  <si>
+    <t>Goia Darius-Ioan</t>
+  </si>
+  <si>
+    <t>MyDrinkShop</t>
+  </si>
+  <si>
+    <t>Se cere realizarea unei aplicații software pentru gestionarea activității unui drinks shop, care să permită
+administrarea produselor vândute (băuturi), a ingredientelor utilizate, a rețetelor de preparare și a comenzilor
+plasate de clienți. La pornirea sistemului, aplicația trebuie să verifice existența fișierelor de date și să le inițializeze;
+dacă acestea nu există, vor fi create automat pentru a asigura starea inițială a sistemului.
+Aplicația trebuie să ofere funcționalități complete de gestiune, să asigure persistența datelor în fișiere, precum
+și o interfață grafică pentru utilizator care să permită navigarea facilă prin meniuri dedicate și timpi de răspuns sub
+o secundă pentru operațiunile de filtrare.
+Soluția trebuie implementată respectând principiile programării orientate pe obiect și o arhitectură stratificată,
+care separă clar:
+• modelul de date,
+• logica de business,
+• accesul la date,
+• interfața cu utilizatorul.</t>
+  </si>
+  <si>
+    <t>1. Aplicația trebuie să permită gestionarea produselor (băuturi):</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>F01.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> adăugarea unui produs nou (nume, pret, categorie, tip, reteta);</t>
+    </r>
   </si>
   <si>
     <t>Observații</t>
@@ -235,189 +284,6 @@
     </r>
   </si>
   <si>
-    <t>EC Identification</t>
-  </si>
-  <si>
-    <t>EC-based TCs</t>
-  </si>
-  <si>
-    <t>No. EC</t>
-  </si>
-  <si>
-    <t>Condition</t>
-  </si>
-  <si>
-    <t>Valid EC</t>
-  </si>
-  <si>
-    <t>Non-valid EC</t>
-  </si>
-  <si>
-    <t>No. TCxx_EC</t>
-  </si>
-  <si>
-    <t>EC</t>
-  </si>
-  <si>
-    <t>input data</t>
-  </si>
-  <si>
-    <t>output data</t>
-  </si>
-  <si>
-    <t>categorie</t>
-  </si>
-  <si>
-    <t>expected</t>
-  </si>
-  <si>
-    <t>2,3,2</t>
-  </si>
-  <si>
-    <t>record added</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>""</t>
-  </si>
-  <si>
-    <t>Error message-? Compiler checked</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>BVA Condition</t>
-  </si>
-  <si>
-    <t>BVA Condition-based TCs</t>
-  </si>
-  <si>
-    <t>Crt. No.</t>
-  </si>
-  <si>
-    <t>No TCxx_BVA</t>
-  </si>
-  <si>
-    <t>BVA condition</t>
-  </si>
-  <si>
-    <t>Correlated TC</t>
-  </si>
-  <si>
-    <t>Executable</t>
-  </si>
-  <si>
-    <t>expected result</t>
-  </si>
-  <si>
-    <t>TC3_EC</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>BBT TCs</t>
-  </si>
-  <si>
-    <t>Final        TC No.</t>
-  </si>
-  <si>
-    <t>Req. ID</t>
-  </si>
-  <si>
-    <t>ECP TCs</t>
-  </si>
-  <si>
-    <t>BVA TCs</t>
-  </si>
-  <si>
-    <t>actual result</t>
-  </si>
-  <si>
-    <t>F01</t>
-  </si>
-  <si>
-    <t>TC3_BVA</t>
-  </si>
-  <si>
-    <t>TC4_BVA</t>
-  </si>
-  <si>
-    <t>TC5_BVA</t>
-  </si>
-  <si>
-    <t>Statistics</t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>Debugging</t>
-  </si>
-  <si>
-    <t>Re-testing</t>
-  </si>
-  <si>
-    <t>Regression Testing</t>
-  </si>
-  <si>
-    <t>#TCs to be run</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">#TCs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="17"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>passed</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">#TCs    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>failed</t>
-    </r>
-  </si>
-  <si>
-    <t>#Bugs</t>
-  </si>
-  <si>
-    <t>#Fixed Bugs</t>
-  </si>
-  <si>
-    <t>Re-tested</t>
-  </si>
-  <si>
-    <t>not yet</t>
-  </si>
-  <si>
-    <t>George Dan-Cristian</t>
-  </si>
-  <si>
-    <t>Grava Bianca-Adelina</t>
-  </si>
-  <si>
-    <t>Goia Darius-Ioan</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -440,109 +306,226 @@
     </r>
   </si>
   <si>
+    <t>EC Identification</t>
+  </si>
+  <si>
+    <t>EC-based TCs</t>
+  </si>
+  <si>
+    <t>No. EC</t>
+  </si>
+  <si>
+    <t>Condition</t>
+  </si>
+  <si>
+    <t>Valid EC</t>
+  </si>
+  <si>
+    <t>Non-valid EC</t>
+  </si>
+  <si>
+    <t>No. TCxx_EC</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>input data</t>
+  </si>
+  <si>
+    <t>output data</t>
+  </si>
+  <si>
+    <t>nume is String, 0 &lt; nume.length &lt; 256</t>
+  </si>
+  <si>
     <t>nume not String</t>
   </si>
   <si>
+    <t>nume</t>
+  </si>
+  <si>
+    <t>pret</t>
+  </si>
+  <si>
+    <t>categorie</t>
+  </si>
+  <si>
+    <t>tip</t>
+  </si>
+  <si>
+    <t>reteta</t>
+  </si>
+  <si>
+    <t>preconditie</t>
+  </si>
+  <si>
+    <t>expected</t>
+  </si>
+  <si>
     <t>nume.length &lt;= 0</t>
   </si>
   <si>
+    <t>3, 6, 8, 10, 15</t>
+  </si>
+  <si>
+    <t>"Fresh Orange"</t>
+  </si>
+  <si>
+    <t>Juice</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>R101</t>
+  </si>
+  <si>
+    <t>reteta exista, neutilizata</t>
+  </si>
+  <si>
+    <t>2,3,2</t>
+  </si>
+  <si>
+    <t>record added</t>
+  </si>
+  <si>
+    <t>0 &lt; nume.length &lt; 256</t>
+  </si>
+  <si>
+    <t>1, 6, 8, 10, 15</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Error message-? Compiler checked</t>
+  </si>
+  <si>
+    <t>nume.length &gt;= 256</t>
+  </si>
+  <si>
+    <t>2, 6, 8, 10, 15</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t>Error message - Empty name</t>
+  </si>
+  <si>
+    <t>pret is number, pret &gt; 0</t>
+  </si>
+  <si>
     <t>pret not number</t>
   </si>
   <si>
+    <t>4, 6, 8, 10, 15</t>
+  </si>
+  <si>
+    <t>"a"  * 300</t>
+  </si>
+  <si>
+    <t>Error message - Name must have less than 256 characters</t>
+  </si>
+  <si>
     <t>pret &gt; 0</t>
   </si>
   <si>
+    <t>3, 5, 8, 10, 15</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>Error message - Invalid price format</t>
+  </si>
+  <si>
     <t>pret &lt;= 0</t>
   </si>
   <si>
-    <t>0 &lt; nume.length &lt; 256</t>
-  </si>
-  <si>
-    <t>nume.length &gt;= 256</t>
+    <t>3, 7, 8, 10, 15</t>
+  </si>
+  <si>
+    <t>Error message - Price must be &gt; 0</t>
+  </si>
+  <si>
+    <t>categorie is CategorieBautura</t>
+  </si>
+  <si>
+    <t>3, 6, 9, 10, 15</t>
+  </si>
+  <si>
+    <t>categorie not CategorieBautura</t>
+  </si>
+  <si>
+    <t>3, 6, 8, 11, 15</t>
+  </si>
+  <si>
+    <t>tip is TipBautura</t>
+  </si>
+  <si>
+    <t>3, 6, 8, 10, 12</t>
+  </si>
+  <si>
+    <t>tip not TipBautura</t>
+  </si>
+  <si>
+    <t>3, 6, 8, 10, 13</t>
+  </si>
+  <si>
+    <t>R301</t>
+  </si>
+  <si>
+    <t>reteta inexistenta</t>
+  </si>
+  <si>
+    <t>Error message - Invalid recipe</t>
+  </si>
+  <si>
+    <t>reteta is Reteta, exista si nu e asociata unui produs</t>
   </si>
   <si>
     <t>reteta not Reteta</t>
   </si>
   <si>
-    <t>reteta inexistenta</t>
+    <t>3, 6, 8, 10, 14</t>
+  </si>
+  <si>
+    <t>R201</t>
+  </si>
+  <si>
+    <t>reteta exista, dar este folosita</t>
+  </si>
+  <si>
+    <t>Error message - Recipe already used</t>
+  </si>
+  <si>
+    <t>reteta deja asociata altui produs</t>
   </si>
   <si>
     <t>reteta neutilizata</t>
   </si>
   <si>
-    <t>reteta deja asociata altui produs</t>
-  </si>
-  <si>
-    <t>nume</t>
-  </si>
-  <si>
-    <t>pret</t>
-  </si>
-  <si>
-    <t>tip</t>
-  </si>
-  <si>
-    <t>reteta</t>
-  </si>
-  <si>
-    <t>preconditie</t>
-  </si>
-  <si>
-    <t>"Fresh Orange"</t>
-  </si>
-  <si>
-    <t>R101</t>
-  </si>
-  <si>
-    <t>reteta exista, neutilizata</t>
-  </si>
-  <si>
-    <t>Error message - Empty name</t>
-  </si>
-  <si>
-    <t>"a"  * 300</t>
-  </si>
-  <si>
-    <t>Error message - Name must have less than 256 characters</t>
-  </si>
-  <si>
-    <t>categorie is CategorieBautura</t>
-  </si>
-  <si>
-    <t>categorie not CategorieBautura</t>
-  </si>
-  <si>
-    <t>tip is TipBautura</t>
-  </si>
-  <si>
-    <t>tip not TipBautura</t>
-  </si>
-  <si>
-    <t>Juice</t>
-  </si>
-  <si>
-    <t>Basic</t>
-  </si>
-  <si>
-    <t>abc</t>
-  </si>
-  <si>
-    <t>Error message - Invalid price format</t>
-  </si>
-  <si>
-    <t>Error message - Price must be &gt; 0</t>
-  </si>
-  <si>
-    <t>R201</t>
-  </si>
-  <si>
-    <t>reteta exista, dar este folosita</t>
-  </si>
-  <si>
-    <t>Error message - Invalid recipe</t>
-  </si>
-  <si>
-    <t>Error message - Recipe already used</t>
+    <t>BVA Condition</t>
+  </si>
+  <si>
+    <t>BVA Condition-based TCs</t>
+  </si>
+  <si>
+    <t>Crt. No.</t>
+  </si>
+  <si>
+    <t>No TCxx_BVA</t>
+  </si>
+  <si>
+    <t>BVA condition</t>
+  </si>
+  <si>
+    <t>Correlated TC</t>
+  </si>
+  <si>
+    <t>Executable</t>
   </si>
   <si>
     <t>nume is String, length in [1,255]</t>
@@ -551,27 +534,63 @@
     <t>01. nume = "", length = 0</t>
   </si>
   <si>
+    <t>expected result</t>
+  </si>
+  <si>
     <t>02. nume = ?, length = -1</t>
   </si>
   <si>
+    <t>TC3_EC</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>03. nume = "F", length = 1</t>
   </si>
   <si>
+    <t>TC2_EC</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
     <t>04. nume = "F…123", length = 255</t>
   </si>
   <si>
+    <t>TC1_EC</t>
+  </si>
+  <si>
+    <t>"F"</t>
+  </si>
+  <si>
     <t>05. nume = "F…12", length = 254</t>
   </si>
   <si>
+    <t>"F…123"</t>
+  </si>
+  <si>
     <t>06. nume = "F…1234", length = 256</t>
   </si>
   <si>
+    <t>"F…12"</t>
+  </si>
+  <si>
     <t>13. pret = - 0,01</t>
   </si>
   <si>
+    <t>TC4_EC</t>
+  </si>
+  <si>
+    <t>"F…1234"</t>
+  </si>
+  <si>
     <t>14. pret = 0,00</t>
   </si>
   <si>
+    <t>TC6_EC</t>
+  </si>
+  <si>
     <t>15. pret = 0,01</t>
   </si>
   <si>
@@ -581,100 +600,73 @@
     <t>17. pret = DOUBLEMAX</t>
   </si>
   <si>
+    <t>DOUBLEMAX - 1</t>
+  </si>
+  <si>
     <t>18. pret = DOUBLEMAX + 1</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>TC2_EC</t>
-  </si>
-  <si>
-    <t>"F"</t>
-  </si>
-  <si>
-    <t>"F…123"</t>
-  </si>
-  <si>
-    <t>"F…12"</t>
-  </si>
-  <si>
-    <t>"F…1234"</t>
-  </si>
-  <si>
-    <t>TC1_EC</t>
-  </si>
-  <si>
-    <t>TC4_EC</t>
-  </si>
-  <si>
-    <t>DOUBLEMAX - 1</t>
-  </si>
-  <si>
     <t>DOUBLEMAX</t>
   </si>
   <si>
     <t>DOUBLEMAX + 1</t>
   </si>
   <si>
-    <t>TC6_EC</t>
-  </si>
-  <si>
-    <t>pret is number, pret &gt; 0</t>
-  </si>
-  <si>
-    <t>nume is String, 0 &lt; nume.length &lt; 256</t>
-  </si>
-  <si>
-    <t>reteta is Reteta, exista si nu e asociata unui produs</t>
-  </si>
-  <si>
-    <t>3, 6, 8, 10, 15</t>
-  </si>
-  <si>
-    <t>1, 6, 8, 10, 15</t>
-  </si>
-  <si>
-    <t>2, 6, 8, 10, 15</t>
-  </si>
-  <si>
-    <t>4, 6, 8, 10, 15</t>
-  </si>
-  <si>
-    <t>3, 5, 8, 10, 15</t>
-  </si>
-  <si>
-    <t>3, 7, 8, 10, 15</t>
-  </si>
-  <si>
-    <t>3, 6, 9, 10, 15</t>
-  </si>
-  <si>
-    <t>3, 6, 8, 11, 15</t>
-  </si>
-  <si>
-    <t>3, 6, 8, 10, 12</t>
-  </si>
-  <si>
-    <t>3, 6, 8, 10, 13</t>
-  </si>
-  <si>
-    <t>3, 6, 8, 10, 14</t>
-  </si>
-  <si>
-    <t>R301</t>
+    <t>BBT TCs</t>
+  </si>
+  <si>
+    <t>Final        TC No.</t>
+  </si>
+  <si>
+    <t>Req. ID</t>
+  </si>
+  <si>
+    <t>ECP TCs</t>
+  </si>
+  <si>
+    <t>BVA TCs</t>
+  </si>
+  <si>
+    <t>actual result</t>
+  </si>
+  <si>
+    <t>F01</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>TC1_BVA</t>
+  </si>
+  <si>
+    <t>record added / no ValidationException thrown</t>
   </si>
   <si>
     <t>TC5_EC</t>
   </si>
   <si>
+    <t>NumberFormatException thrown before service call</t>
+  </si>
+  <si>
+    <t>TC8_BVA</t>
+  </si>
+  <si>
     <t>TC10_EC</t>
   </si>
   <si>
+    <t>record added; ValidationException was not thrown</t>
+  </si>
+  <si>
     <t>TC11_EC</t>
   </si>
   <si>
-    <t>TC1_BVA</t>
+    <t>TC3_BVA</t>
+  </si>
+  <si>
+    <t>TC4_BVA</t>
+  </si>
+  <si>
+    <t>TC5_BVA</t>
   </si>
   <si>
     <t>TC6_BVA</t>
@@ -683,9 +675,6 @@
     <t>TC7_BVA</t>
   </si>
   <si>
-    <t>TC8_BVA</t>
-  </si>
-  <si>
     <t>TC9_BVA</t>
   </si>
   <si>
@@ -695,51 +684,71 @@
     <t>TC11_BVA</t>
   </si>
   <si>
-    <t>MyDrinkShop</t>
-  </si>
-  <si>
-    <t>1. Aplicația trebuie să permită gestionarea produselor (băuturi):</t>
-  </si>
-  <si>
+    <t>Statistics</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Debugging</t>
+  </si>
+  <si>
+    <t>Re-testing</t>
+  </si>
+  <si>
+    <t>Regression Testing</t>
+  </si>
+  <si>
+    <t>#TCs to be run</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">#TCs </t>
+    </r>
     <r>
       <rPr>
         <b/>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Calibri (Body)"/>
+        <sz val="11"/>
+        <color indexed="17"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
-      <t>F01.</t>
+      <t>passed</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">#TCs    </t>
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Body)"/>
+        <b/>
+        <sz val="11"/>
+        <color indexed="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> adăugarea unui produs nou (nume, pret, categorie, tip, reteta);</t>
+      <t>failed</t>
     </r>
   </si>
   <si>
-    <t>Se cere realizarea unei aplicații software pentru gestionarea activității unui drinks shop, care să permită
-administrarea produselor vândute (băuturi), a ingredientelor utilizate, a rețetelor de preparare și a comenzilor
-plasate de clienți. La pornirea sistemului, aplicația trebuie să verifice existența fișierelor de date și să le inițializeze;
-dacă acestea nu există, vor fi create automat pentru a asigura starea inițială a sistemului.
-Aplicația trebuie să ofere funcționalități complete de gestiune, să asigure persistența datelor în fișiere, precum
-și o interfață grafică pentru utilizator care să permită navigarea facilă prin meniuri dedicate și timpi de răspuns sub
-o secundă pentru operațiunile de filtrare.
-Soluția trebuie implementată respectând principiile programării orientate pe obiect și o arhitectură stratificată,
-care separă clar:
-• modelul de date,
-• logica de business,
-• accesul la date,
-• interfața cu utilizatorul.</t>
+    <t>#Bugs</t>
+  </si>
+  <si>
+    <t>#Fixed Bugs</t>
+  </si>
+  <si>
+    <t>Re-tested</t>
+  </si>
+  <si>
+    <t>not yet</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -950,6 +959,18 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1471,7 +1492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1557,9 +1578,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1599,9 +1617,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1617,57 +1634,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1686,25 +1733,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1719,137 +1775,106 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2158,16 +2183,16 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:O22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="22.5" customWidth="1"/>
-    <col min="9" max="9" width="32.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.5" customWidth="1"/>
-    <col min="12" max="12" width="12.1640625" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+    <col min="9" max="9" width="32.85546875" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:10">
       <c r="C1" s="57" t="s">
         <v>0</v>
       </c>
@@ -2178,18 +2203,18 @@
         <v>1</v>
       </c>
       <c r="I1" s="33"/>
-      <c r="J1" s="134">
+      <c r="J1" s="54">
         <v>46103</v>
       </c>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:10">
       <c r="H2" s="60" t="s">
         <v>2</v>
       </c>
       <c r="I2" s="60"/>
       <c r="J2" s="60"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:10">
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
         <v>3</v>
@@ -2198,112 +2223,112 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:10">
       <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="J4" s="2">
         <v>233</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:10">
       <c r="H5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="J5" s="2">
         <v>233</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:10">
       <c r="B6" s="19"/>
       <c r="H6" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="J6" s="2">
         <v>233</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="2:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="B8" s="139" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" ht="220" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="138" t="s">
-        <v>157</v>
-      </c>
-      <c r="C9" s="138"/>
-      <c r="D9" s="138"/>
-      <c r="E9" s="138"/>
-      <c r="F9" s="138"/>
-      <c r="G9" s="138"/>
-      <c r="H9" s="138"/>
-      <c r="I9" s="138"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:10" ht="14.45" customHeight="1"/>
+    <row r="8" spans="2:10" ht="15.95">
+      <c r="B8" s="55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="219.95" customHeight="1">
+      <c r="B9" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+    </row>
+    <row r="10" spans="2:10">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B11" s="136" t="s">
-        <v>155</v>
-      </c>
-      <c r="C11" s="136"/>
-      <c r="D11" s="136"/>
-      <c r="E11" s="136"/>
-      <c r="F11" s="136"/>
-      <c r="G11" s="136"/>
-    </row>
-    <row r="12" spans="2:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="B12" s="137" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12" s="137"/>
-      <c r="D12" s="137"/>
-      <c r="E12" s="137"/>
-      <c r="F12" s="137"/>
-      <c r="G12" s="137"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:10">
+      <c r="B11" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+    </row>
+    <row r="12" spans="2:10" ht="15.95">
+      <c r="B12" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+    </row>
+    <row r="13" spans="2:10">
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:10">
       <c r="B14" s="31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10">
       <c r="B15" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10">
       <c r="C16" s="29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="B17" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="B18" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -2318,9 +2343,9 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15">
       <c r="B19" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -2335,10 +2360,10 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" ht="14.45" customHeight="1">
       <c r="A20" s="30"/>
       <c r="B20" s="56" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C20" s="56"/>
       <c r="D20" s="56"/>
@@ -2353,7 +2378,7 @@
       <c r="M20" s="56"/>
       <c r="N20" s="56"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15">
       <c r="C22" s="32"/>
     </row>
   </sheetData>
@@ -2376,26 +2401,26 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:Q25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" customWidth="1"/>
     <col min="5" max="5" width="27" customWidth="1"/>
-    <col min="6" max="6" width="5.83203125" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="25.1640625" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5" customWidth="1"/>
-    <col min="16" max="16" width="29.5" customWidth="1"/>
-    <col min="17" max="17" width="19.6640625" customWidth="1"/>
+    <col min="10" max="10" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" customWidth="1"/>
+    <col min="16" max="16" width="29.42578125" customWidth="1"/>
+    <col min="17" max="17" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:17">
       <c r="B1" s="57" t="s">
         <v>0</v>
       </c>
@@ -2403,633 +2428,637 @@
       <c r="D1" s="58"/>
       <c r="E1" s="59"/>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B3" s="69" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="71"/>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B5" s="72" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="G5" s="73" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
-      <c r="M5" s="73"/>
-      <c r="N5" s="73"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="73"/>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:17">
+      <c r="B3" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="81"/>
+    </row>
+    <row r="5" spans="2:17">
+      <c r="B5" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="G5" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="83"/>
+      <c r="O5" s="83"/>
+      <c r="P5" s="83"/>
+      <c r="Q5" s="83"/>
+    </row>
+    <row r="6" spans="2:17">
       <c r="B6" s="10" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="74" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="80" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="83"/>
-      <c r="O6" s="79"/>
-      <c r="P6" s="82" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q6" s="82"/>
-    </row>
-    <row r="7" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="G6" s="84" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="90" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="93"/>
+      <c r="K6" s="93"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="93"/>
+      <c r="N6" s="93"/>
+      <c r="O6" s="89"/>
+      <c r="P6" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6" s="92"/>
+    </row>
+    <row r="7" spans="2:17" ht="15" customHeight="1">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="63" t="s">
-        <v>130</v>
+      <c r="C7" s="75" t="s">
+        <v>33</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="75"/>
-      <c r="H7" s="81"/>
+        <v>34</v>
+      </c>
+      <c r="G7" s="85"/>
+      <c r="H7" s="91"/>
       <c r="I7" s="10" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="N7" s="78" t="s">
-        <v>84</v>
-      </c>
-      <c r="O7" s="79"/>
-      <c r="P7" s="78" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q7" s="79"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+      <c r="N7" s="88" t="s">
+        <v>40</v>
+      </c>
+      <c r="O7" s="89"/>
+      <c r="P7" s="88" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q7" s="89"/>
+    </row>
+    <row r="8" spans="2:17">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="64"/>
+      <c r="C8" s="76"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="G8" s="10">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="J8" s="2">
         <v>12.5</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N8" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="O8" s="62" t="s">
-        <v>27</v>
-      </c>
-      <c r="P8" s="61" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q8" s="62"/>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="N8" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="O8" s="66" t="s">
+        <v>49</v>
+      </c>
+      <c r="P8" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q8" s="66"/>
+    </row>
+    <row r="9" spans="2:17">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="64"/>
+      <c r="C9" s="76"/>
       <c r="D9" s="4" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="E9" s="4"/>
       <c r="G9" s="10">
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="J9" s="2">
         <v>12.5</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N9" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="O9" s="62" t="s">
-        <v>27</v>
-      </c>
-      <c r="P9" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q9" s="77"/>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="N9" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="O9" s="66" t="s">
+        <v>49</v>
+      </c>
+      <c r="P9" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q9" s="74"/>
+    </row>
+    <row r="10" spans="2:17">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="65"/>
+      <c r="C10" s="86"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G10" s="10">
         <v>3</v>
       </c>
-      <c r="H10" s="50" t="s">
-        <v>134</v>
+      <c r="H10" s="49" t="s">
+        <v>56</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="J10" s="2">
         <v>12.5</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N10" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="O10" s="62" t="s">
-        <v>27</v>
-      </c>
-      <c r="P10" s="61" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q10" s="62"/>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="N10" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="O10" s="66" t="s">
+        <v>49</v>
+      </c>
+      <c r="P10" s="65" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q10" s="66"/>
+    </row>
+    <row r="11" spans="2:17">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="66" t="s">
-        <v>129</v>
+      <c r="C11" s="77" t="s">
+        <v>59</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G11" s="10">
         <v>4</v>
       </c>
-      <c r="H11" s="50" t="s">
-        <v>135</v>
+      <c r="H11" s="49" t="s">
+        <v>61</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="J11" s="2">
         <v>12.5</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N11" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="O11" s="62"/>
-      <c r="P11" s="61" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q11" s="62"/>
-    </row>
-    <row r="12" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="N11" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="O11" s="66"/>
+      <c r="P11" s="65" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q11" s="66"/>
+    </row>
+    <row r="12" spans="2:17" ht="15" customHeight="1">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="67"/>
+      <c r="C12" s="87"/>
       <c r="D12" s="4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E12" s="4"/>
       <c r="G12" s="10">
         <v>5</v>
       </c>
-      <c r="H12" s="50" t="s">
-        <v>136</v>
+      <c r="H12" s="49" t="s">
+        <v>65</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N12" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="O12" s="62"/>
-      <c r="P12" s="61" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q12" s="62"/>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="N12" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="O12" s="66"/>
+      <c r="P12" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q12" s="66"/>
+    </row>
+    <row r="13" spans="2:17">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="68"/>
+      <c r="C13" s="78"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G13" s="10">
         <v>6</v>
       </c>
-      <c r="H13" s="50" t="s">
-        <v>137</v>
+      <c r="H13" s="49" t="s">
+        <v>69</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="J13" s="2">
         <v>0</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N13" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="O13" s="62"/>
-      <c r="P13" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q13" s="62"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="N13" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="O13" s="66"/>
+      <c r="P13" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q13" s="66"/>
+    </row>
+    <row r="14" spans="2:17">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="66" t="s">
-        <v>91</v>
+      <c r="C14" s="77" t="s">
+        <v>71</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E14" s="4"/>
       <c r="G14" s="10">
         <v>7</v>
       </c>
-      <c r="H14" s="50" t="s">
-        <v>138</v>
+      <c r="H14" s="49" t="s">
+        <v>72</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="J14" s="2">
         <v>12.5</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N14" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="O14" s="62"/>
-      <c r="P14" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q14" s="77"/>
-    </row>
-    <row r="15" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="N14" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="O14" s="66"/>
+      <c r="P14" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q14" s="74"/>
+    </row>
+    <row r="15" spans="2:17" ht="15" customHeight="1">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="68"/>
+      <c r="C15" s="78"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="G15" s="10">
         <v>8</v>
       </c>
-      <c r="H15" s="50" t="s">
-        <v>139</v>
+      <c r="H15" s="49" t="s">
+        <v>74</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="J15" s="2">
         <v>12.5</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N15" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="O15" s="62"/>
-      <c r="P15" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q15" s="77"/>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="N15" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="O15" s="66"/>
+      <c r="P15" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q15" s="74"/>
+    </row>
+    <row r="16" spans="2:17">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="66" t="s">
-        <v>93</v>
+      <c r="C16" s="77" t="s">
+        <v>75</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="E16" s="4"/>
       <c r="G16" s="10">
         <v>9</v>
       </c>
-      <c r="H16" s="50" t="s">
-        <v>140</v>
+      <c r="H16" s="49" t="s">
+        <v>76</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="J16" s="2">
         <v>12.5</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N16" s="61"/>
-      <c r="O16" s="62"/>
-      <c r="P16" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q16" s="77"/>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+      <c r="N16" s="65"/>
+      <c r="O16" s="66"/>
+      <c r="P16" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q16" s="74"/>
+    </row>
+    <row r="17" spans="2:17">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="68"/>
+      <c r="C17" s="78"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="G17" s="10">
         <v>10</v>
       </c>
-      <c r="H17" s="50" t="s">
-        <v>141</v>
+      <c r="H17" s="49" t="s">
+        <v>78</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="J17" s="2">
         <v>12.5</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="N17" s="61" t="s">
-        <v>77</v>
-      </c>
-      <c r="O17" s="62"/>
-      <c r="P17" s="61" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q17" s="62"/>
-    </row>
-    <row r="18" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+      <c r="N17" s="65" t="s">
+        <v>80</v>
+      </c>
+      <c r="O17" s="66"/>
+      <c r="P17" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q17" s="66"/>
+    </row>
+    <row r="18" spans="2:17" ht="15" customHeight="1">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="63" t="s">
-        <v>131</v>
+      <c r="C18" s="75" t="s">
+        <v>82</v>
       </c>
       <c r="D18" s="34"/>
       <c r="E18" s="34" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G18" s="36">
         <v>11</v>
       </c>
-      <c r="H18" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="I18" s="41" t="s">
+      <c r="H18" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="I18" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="40">
+        <v>12.5</v>
+      </c>
+      <c r="K18" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="L18" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="M18" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="J18" s="41">
-        <v>12.5</v>
-      </c>
-      <c r="K18" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="L18" s="41" t="s">
-        <v>96</v>
-      </c>
-      <c r="M18" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="N18" s="85" t="s">
-        <v>101</v>
-      </c>
-      <c r="O18" s="86"/>
-      <c r="P18" s="85" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q18" s="86"/>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="N18" s="67" t="s">
+        <v>86</v>
+      </c>
+      <c r="O18" s="68"/>
+      <c r="P18" s="67" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q18" s="68"/>
+    </row>
+    <row r="19" spans="2:17">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="64"/>
+      <c r="C19" s="76"/>
       <c r="D19" s="4"/>
       <c r="E19" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="G19" s="52"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="90"/>
-      <c r="O19" s="90"/>
-      <c r="P19" s="88"/>
-      <c r="Q19" s="88"/>
-    </row>
-    <row r="20" spans="2:17" ht="16" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+      <c r="G19" s="51"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="72"/>
+      <c r="O19" s="72"/>
+      <c r="P19" s="70"/>
+      <c r="Q19" s="70"/>
+    </row>
+    <row r="20" spans="2:17" ht="15.95">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="64"/>
+      <c r="C20" s="76"/>
       <c r="D20" s="34"/>
-      <c r="E20" s="38" t="s">
-        <v>79</v>
+      <c r="E20" s="37" t="s">
+        <v>88</v>
       </c>
       <c r="G20" s="14"/>
-      <c r="N20" s="87"/>
-      <c r="O20" s="87"/>
-      <c r="P20" s="89"/>
-      <c r="Q20" s="89"/>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="N20" s="69"/>
+      <c r="O20" s="69"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+    </row>
+    <row r="21" spans="2:17">
       <c r="B21" s="35">
         <v>15</v>
       </c>
-      <c r="C21" s="64"/>
-      <c r="D21" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" s="49"/>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B22" s="42"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="C21" s="76"/>
+      <c r="D21" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="48"/>
+    </row>
+    <row r="22" spans="2:17">
+      <c r="B22" s="41"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+    </row>
+    <row r="23" spans="2:17">
       <c r="B23" s="6"/>
-      <c r="C23" s="43"/>
+      <c r="C23" s="42"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="84"/>
-      <c r="G23" s="84"/>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="E23" s="39"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="6"/>
-      <c r="C24" s="43"/>
+      <c r="C24" s="42"/>
       <c r="D24" s="3"/>
       <c r="E24" s="6"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:17">
       <c r="B25" s="6"/>
-      <c r="C25" s="43"/>
+      <c r="C25" s="42"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="40"/>
+      <c r="E25" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P7:Q7"/>
     <mergeCell ref="C18:C21"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="C14:C15"/>
@@ -3046,21 +3075,17 @@
     <mergeCell ref="P15:Q15"/>
     <mergeCell ref="N14:O14"/>
     <mergeCell ref="N11:O11"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="P16:Q16"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3074,27 +3099,27 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:R30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.5" customWidth="1"/>
-    <col min="7" max="7" width="9.5" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.6640625" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.1640625" customWidth="1"/>
-    <col min="17" max="17" width="23.33203125" customWidth="1"/>
-    <col min="18" max="18" width="28.83203125" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.140625" customWidth="1"/>
+    <col min="17" max="17" width="23.28515625" customWidth="1"/>
+    <col min="18" max="18" width="28.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:18">
       <c r="B1" s="57" t="s">
         <v>0</v>
       </c>
@@ -3102,571 +3127,571 @@
       <c r="D1" s="58"/>
       <c r="E1" s="59"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B3" s="69" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="71"/>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B5" s="97" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
+    <row r="3" spans="2:18">
+      <c r="B3" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="81"/>
+    </row>
+    <row r="5" spans="2:18">
+      <c r="B5" s="101" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="73" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
-      <c r="M5" s="73"/>
-      <c r="N5" s="73"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="73"/>
-      <c r="R5" s="73"/>
-    </row>
-    <row r="6" spans="2:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G5" s="83" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="83"/>
+      <c r="O5" s="83"/>
+      <c r="P5" s="83"/>
+      <c r="Q5" s="83"/>
+      <c r="R5" s="83"/>
+    </row>
+    <row r="6" spans="2:18" ht="14.45" customHeight="1">
       <c r="B6" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="G6" s="104" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="I6" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="J6" s="106" t="s">
+        <v>96</v>
+      </c>
+      <c r="K6" s="94" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="95"/>
+      <c r="M6" s="95"/>
+      <c r="N6" s="95"/>
+      <c r="O6" s="95"/>
+      <c r="P6" s="96"/>
+      <c r="Q6" s="102" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" s="103"/>
+    </row>
+    <row r="7" spans="2:18" ht="15.95">
+      <c r="B7" s="77">
+        <v>1</v>
+      </c>
+      <c r="C7" s="75" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="G6" s="91" t="s">
+      <c r="L7" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="91" t="s">
+      <c r="M7" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="91" t="s">
+      <c r="N7" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="93" t="s">
+      <c r="O7" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="102" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="103"/>
-      <c r="M6" s="103"/>
-      <c r="N6" s="103"/>
-      <c r="O6" s="103"/>
-      <c r="P6" s="104"/>
-      <c r="Q6" s="98" t="s">
-        <v>24</v>
-      </c>
-      <c r="R6" s="99"/>
-    </row>
-    <row r="7" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7" s="66">
-        <v>1</v>
-      </c>
-      <c r="C7" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="46" t="s">
-        <v>80</v>
-      </c>
-      <c r="L7" s="46" t="s">
-        <v>81</v>
-      </c>
-      <c r="M7" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="N7" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="O7" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="P7" s="46" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q7" s="78" t="s">
+      <c r="P7" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="R7" s="79"/>
-    </row>
-    <row r="8" spans="2:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="67"/>
-      <c r="C8" s="64"/>
+      <c r="Q7" s="88" t="s">
+        <v>99</v>
+      </c>
+      <c r="R7" s="89"/>
+    </row>
+    <row r="8" spans="2:18" ht="15.95" customHeight="1">
+      <c r="B8" s="87"/>
+      <c r="C8" s="76"/>
       <c r="D8" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G8" s="46">
+        <v>100</v>
+      </c>
+      <c r="G8" s="45">
         <v>1</v>
       </c>
       <c r="H8" s="9">
         <v>1</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="K8" s="18" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="L8" s="18">
         <v>12.5</v>
       </c>
       <c r="M8" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="P8" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q8" s="100" t="s">
-        <v>88</v>
-      </c>
-      <c r="R8" s="101"/>
-    </row>
-    <row r="9" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B9" s="67"/>
-      <c r="C9" s="64"/>
+        <v>47</v>
+      </c>
+      <c r="P8" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q8" s="97" t="s">
+        <v>58</v>
+      </c>
+      <c r="R8" s="98"/>
+    </row>
+    <row r="9" spans="2:18" ht="15.95">
+      <c r="B9" s="87"/>
+      <c r="C9" s="76"/>
       <c r="D9" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G9" s="46">
+        <v>103</v>
+      </c>
+      <c r="G9" s="45">
         <v>2</v>
       </c>
       <c r="H9" s="9">
         <v>2</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="L9" s="18">
         <v>12.5</v>
       </c>
       <c r="M9" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="P9" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q9" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="R9" s="77"/>
-    </row>
-    <row r="10" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B10" s="67"/>
-      <c r="C10" s="64"/>
+        <v>47</v>
+      </c>
+      <c r="P9" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q9" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="R9" s="74"/>
+    </row>
+    <row r="10" spans="2:18" ht="15.95">
+      <c r="B10" s="87"/>
+      <c r="C10" s="76"/>
       <c r="D10" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G10" s="46">
+        <v>106</v>
+      </c>
+      <c r="G10" s="45">
         <v>3</v>
       </c>
       <c r="H10" s="9">
         <v>3</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="L10" s="18">
         <v>12.5</v>
       </c>
       <c r="M10" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="P10" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q10" s="100" t="s">
-        <v>28</v>
-      </c>
-      <c r="R10" s="101"/>
-    </row>
-    <row r="11" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B11" s="67"/>
-      <c r="C11" s="64"/>
+        <v>47</v>
+      </c>
+      <c r="P10" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q10" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="R10" s="98"/>
+    </row>
+    <row r="11" spans="2:18" ht="15.95">
+      <c r="B11" s="87"/>
+      <c r="C11" s="76"/>
       <c r="D11" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G11" s="46">
+      <c r="G11" s="45">
         <v>4</v>
       </c>
       <c r="H11" s="9">
         <v>4</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="L11" s="18">
         <v>12.5</v>
       </c>
       <c r="M11" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="P11" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q11" s="100" t="s">
-        <v>28</v>
-      </c>
-      <c r="R11" s="101"/>
-    </row>
-    <row r="12" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B12" s="68"/>
-      <c r="C12" s="65"/>
+        <v>47</v>
+      </c>
+      <c r="P11" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q11" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="R11" s="98"/>
+    </row>
+    <row r="12" spans="2:18" ht="15.95">
+      <c r="B12" s="78"/>
+      <c r="C12" s="86"/>
       <c r="D12" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G12" s="46">
+        <v>111</v>
+      </c>
+      <c r="G12" s="45">
         <v>5</v>
       </c>
       <c r="H12" s="9">
         <v>5</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="L12" s="18">
         <v>12.5</v>
       </c>
       <c r="M12" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="N12" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="P12" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q12" s="100" t="s">
-        <v>28</v>
-      </c>
-      <c r="R12" s="101"/>
-    </row>
-    <row r="13" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B13" s="66">
+        <v>47</v>
+      </c>
+      <c r="P12" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q12" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="R12" s="98"/>
+    </row>
+    <row r="13" spans="2:18" ht="15.95">
+      <c r="B13" s="77">
         <v>2</v>
       </c>
-      <c r="C13" s="63" t="s">
-        <v>129</v>
+      <c r="C13" s="75" t="s">
+        <v>59</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G13" s="46">
+        <v>113</v>
+      </c>
+      <c r="G13" s="45">
         <v>6</v>
       </c>
       <c r="H13" s="9">
         <v>6</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="L13" s="18">
         <v>12.5</v>
       </c>
       <c r="M13" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="P13" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q13" s="61" t="s">
-        <v>90</v>
-      </c>
-      <c r="R13" s="62"/>
-    </row>
-    <row r="14" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B14" s="67"/>
-      <c r="C14" s="64"/>
+        <v>47</v>
+      </c>
+      <c r="P13" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q13" s="65" t="s">
+        <v>63</v>
+      </c>
+      <c r="R13" s="66"/>
+    </row>
+    <row r="14" spans="2:18" ht="15.95">
+      <c r="B14" s="87"/>
+      <c r="C14" s="76"/>
       <c r="D14" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G14" s="46">
+        <v>116</v>
+      </c>
+      <c r="G14" s="45">
         <v>7</v>
       </c>
       <c r="H14" s="9">
         <v>7</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="K14" s="18" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="L14" s="18">
         <v>-0.01</v>
       </c>
       <c r="M14" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="N14" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="P14" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q14" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="R14" s="62"/>
-    </row>
-    <row r="15" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B15" s="67"/>
-      <c r="C15" s="64"/>
+        <v>47</v>
+      </c>
+      <c r="P14" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q14" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="R14" s="66"/>
+    </row>
+    <row r="15" spans="2:18" ht="15.95">
+      <c r="B15" s="87"/>
+      <c r="C15" s="76"/>
       <c r="D15" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G15" s="46">
+        <v>118</v>
+      </c>
+      <c r="G15" s="45">
         <v>8</v>
       </c>
       <c r="H15" s="9">
         <v>8</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="K15" s="18" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="L15" s="18">
         <v>0</v>
       </c>
       <c r="M15" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="P15" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q15" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="R15" s="62"/>
-    </row>
-    <row r="16" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B16" s="67"/>
-      <c r="C16" s="64"/>
+        <v>47</v>
+      </c>
+      <c r="P15" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q15" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="R15" s="66"/>
+    </row>
+    <row r="16" spans="2:18" ht="15.95">
+      <c r="B16" s="87"/>
+      <c r="C16" s="76"/>
       <c r="D16" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G16" s="46">
+        <v>119</v>
+      </c>
+      <c r="G16" s="45">
         <v>9</v>
       </c>
       <c r="H16" s="9">
         <v>9</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="K16" s="18" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="L16" s="18">
         <v>0.01</v>
       </c>
       <c r="M16" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="P16" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q16" s="100" t="s">
-        <v>28</v>
-      </c>
-      <c r="R16" s="101"/>
-    </row>
-    <row r="17" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B17" s="67"/>
-      <c r="C17" s="64"/>
+        <v>47</v>
+      </c>
+      <c r="P16" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q16" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="R16" s="98"/>
+    </row>
+    <row r="17" spans="2:18" ht="15.95">
+      <c r="B17" s="87"/>
+      <c r="C17" s="76"/>
       <c r="D17" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G17" s="46">
+        <v>120</v>
+      </c>
+      <c r="G17" s="45">
         <v>10</v>
       </c>
       <c r="H17" s="9">
         <v>10</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="K17" s="18" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="M17" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="O17" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="P17" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q17" s="100" t="s">
-        <v>28</v>
-      </c>
-      <c r="R17" s="101"/>
-    </row>
-    <row r="18" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B18" s="67"/>
-      <c r="C18" s="64"/>
-      <c r="D18" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="G18" s="46">
+        <v>47</v>
+      </c>
+      <c r="P17" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q17" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="R17" s="98"/>
+    </row>
+    <row r="18" spans="2:18" ht="15.95">
+      <c r="B18" s="87"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="G18" s="45">
         <v>11</v>
       </c>
       <c r="H18" s="9">
         <v>11</v>
       </c>
       <c r="I18" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="L18" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="J18" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="K18" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="L18" s="18" t="s">
-        <v>126</v>
-      </c>
       <c r="M18" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="N18" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="P18" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q18" s="100" t="s">
-        <v>28</v>
-      </c>
-      <c r="R18" s="101"/>
-    </row>
-    <row r="19" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B19" s="45"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="42"/>
-      <c r="G19" s="46">
+        <v>47</v>
+      </c>
+      <c r="P18" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q18" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="R18" s="98"/>
+    </row>
+    <row r="19" spans="2:18" ht="15.95">
+      <c r="B19" s="44"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="41"/>
+      <c r="G19" s="45">
         <v>12</v>
       </c>
       <c r="H19" s="9">
@@ -3674,35 +3699,35 @@
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="L19" s="18" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="M19" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="N19" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="O19" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="P19" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q19" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="R19" s="77"/>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="P19" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q19" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="R19" s="74"/>
+    </row>
+    <row r="20" spans="2:18">
       <c r="B20" s="30"/>
-      <c r="C20" s="43"/>
-      <c r="G20" s="46">
+      <c r="C20" s="42"/>
+      <c r="G20" s="45">
         <v>13</v>
       </c>
       <c r="H20" s="9"/>
@@ -3714,13 +3739,13 @@
       <c r="N20" s="18"/>
       <c r="O20" s="18"/>
       <c r="P20" s="18"/>
-      <c r="Q20" s="100"/>
-      <c r="R20" s="101"/>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q20" s="97"/>
+      <c r="R20" s="98"/>
+    </row>
+    <row r="21" spans="2:18">
       <c r="B21" s="30"/>
-      <c r="C21" s="43"/>
-      <c r="G21" s="46">
+      <c r="C21" s="42"/>
+      <c r="G21" s="45">
         <v>14</v>
       </c>
       <c r="H21" s="9"/>
@@ -3732,13 +3757,13 @@
       <c r="N21" s="18"/>
       <c r="O21" s="18"/>
       <c r="P21" s="18"/>
-      <c r="Q21" s="100"/>
-      <c r="R21" s="101"/>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q21" s="97"/>
+      <c r="R21" s="98"/>
+    </row>
+    <row r="22" spans="2:18">
       <c r="B22" s="30"/>
-      <c r="C22" s="43"/>
-      <c r="G22" s="46">
+      <c r="C22" s="42"/>
+      <c r="G22" s="45">
         <v>15</v>
       </c>
       <c r="H22" s="9"/>
@@ -3750,13 +3775,13 @@
       <c r="N22" s="18"/>
       <c r="O22" s="18"/>
       <c r="P22" s="18"/>
-      <c r="Q22" s="100"/>
-      <c r="R22" s="101"/>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q22" s="97"/>
+      <c r="R22" s="98"/>
+    </row>
+    <row r="23" spans="2:18">
       <c r="B23" s="30"/>
-      <c r="C23" s="43"/>
-      <c r="G23" s="46">
+      <c r="C23" s="42"/>
+      <c r="G23" s="45">
         <v>16</v>
       </c>
       <c r="H23" s="9"/>
@@ -3768,13 +3793,13 @@
       <c r="N23" s="18"/>
       <c r="O23" s="18"/>
       <c r="P23" s="18"/>
-      <c r="Q23" s="100"/>
-      <c r="R23" s="101"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q23" s="97"/>
+      <c r="R23" s="98"/>
+    </row>
+    <row r="24" spans="2:18">
       <c r="B24" s="30"/>
-      <c r="C24" s="43"/>
-      <c r="G24" s="46">
+      <c r="C24" s="42"/>
+      <c r="G24" s="45">
         <v>17</v>
       </c>
       <c r="H24" s="9"/>
@@ -3786,13 +3811,13 @@
       <c r="N24" s="18"/>
       <c r="O24" s="18"/>
       <c r="P24" s="18"/>
-      <c r="Q24" s="100"/>
-      <c r="R24" s="101"/>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q24" s="97"/>
+      <c r="R24" s="98"/>
+    </row>
+    <row r="25" spans="2:18">
       <c r="B25" s="30"/>
-      <c r="C25" s="43"/>
-      <c r="G25" s="46">
+      <c r="C25" s="42"/>
+      <c r="G25" s="45">
         <v>18</v>
       </c>
       <c r="H25" s="9"/>
@@ -3804,59 +3829,51 @@
       <c r="N25" s="18"/>
       <c r="O25" s="18"/>
       <c r="P25" s="18"/>
-      <c r="Q25" s="100"/>
-      <c r="R25" s="101"/>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q25" s="97"/>
+      <c r="R25" s="98"/>
+    </row>
+    <row r="26" spans="2:18">
       <c r="B26" s="30"/>
-      <c r="C26" s="43"/>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C26" s="42"/>
+    </row>
+    <row r="27" spans="2:18">
       <c r="B27" s="30"/>
-      <c r="C27" s="43"/>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C27" s="42"/>
+    </row>
+    <row r="28" spans="2:18">
       <c r="B28" s="30"/>
-      <c r="C28" s="43"/>
-      <c r="G28" s="84"/>
-      <c r="H28" s="84"/>
-      <c r="I28" s="96"/>
-      <c r="J28" s="96"/>
-      <c r="K28" s="96"/>
-      <c r="L28" s="96"/>
-      <c r="M28" s="96"/>
+      <c r="C28" s="42"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="100"/>
+      <c r="J28" s="100"/>
+      <c r="K28" s="100"/>
+      <c r="L28" s="100"/>
+      <c r="M28" s="100"/>
       <c r="N28" s="25"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:18">
       <c r="B29" s="30"/>
-      <c r="C29" s="43"/>
-      <c r="I29" s="95"/>
-      <c r="J29" s="95"/>
-      <c r="K29" s="95"/>
-      <c r="L29" s="95"/>
-      <c r="M29" s="95"/>
+      <c r="C29" s="42"/>
+      <c r="I29" s="99"/>
+      <c r="J29" s="99"/>
+      <c r="K29" s="99"/>
+      <c r="L29" s="99"/>
+      <c r="M29" s="99"/>
       <c r="N29" s="26"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:18">
       <c r="B30" s="30"/>
-      <c r="C30" s="43"/>
+      <c r="C30" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C7:C12"/>
     <mergeCell ref="B13:B18"/>
     <mergeCell ref="C13:C18"/>
     <mergeCell ref="I29:M29"/>
@@ -3873,12 +3890,20 @@
     <mergeCell ref="Q15:R15"/>
     <mergeCell ref="Q22:R22"/>
     <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="C7:C12"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q13:R13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3891,19 +3916,19 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="B1:P28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" customWidth="1"/>
-    <col min="9" max="9" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.7109375" customWidth="1"/>
     <col min="13" max="13" width="44" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="14" max="14" width="46.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:14">
       <c r="B1" s="57" t="s">
         <v>0</v>
       </c>
@@ -3911,614 +3936,644 @@
       <c r="D1" s="58"/>
       <c r="E1" s="59"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B3" s="111" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="111"/>
-      <c r="M3" s="111"/>
-      <c r="N3" s="111"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="109" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="115" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="80" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="79"/>
-      <c r="M4" s="82" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" s="82"/>
-    </row>
-    <row r="5" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="114"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="108"/>
+    <row r="3" spans="2:14">
+      <c r="B3" s="136" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="136"/>
+      <c r="M3" s="136"/>
+      <c r="N3" s="136"/>
+    </row>
+    <row r="4" spans="2:14">
+      <c r="B4" s="84" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="134" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="90" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="92"/>
+    </row>
+    <row r="5" spans="2:14" ht="15.95" thickBot="1">
+      <c r="B5" s="119"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="133"/>
       <c r="F5" s="12" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="K5" s="106" t="s">
-        <v>84</v>
-      </c>
-      <c r="L5" s="107"/>
+        <v>39</v>
+      </c>
+      <c r="K5" s="131" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="132"/>
       <c r="M5" s="12" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="N5" s="36" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
       <c r="B6" s="11">
         <v>1</v>
       </c>
-      <c r="C6" s="112" t="s">
-        <v>49</v>
+      <c r="C6" s="116" t="s">
+        <v>131</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="G6" s="2">
         <v>12.5</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K6" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="L6" s="62" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="K6" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="66" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="N6" s="138" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
       <c r="B7" s="11">
         <v>2</v>
       </c>
-      <c r="C7" s="113"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="15" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="G7" s="2">
         <v>12.5</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="K7" s="60" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="L7" s="60" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="N7" s="54"/>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="N7" s="139" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
       <c r="B8" s="11">
         <v>3</v>
       </c>
-      <c r="C8" s="113"/>
+      <c r="C8" s="117"/>
       <c r="D8" s="15" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="G8" s="2">
         <v>12.5</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="K8" s="60" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="L8" s="60"/>
       <c r="M8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="N8" s="54"/>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+      <c r="N8" s="53" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
       <c r="B9" s="7">
         <v>4</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="117"/>
       <c r="D9" s="15" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="K9" s="60" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="L9" s="60"/>
       <c r="M9" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="N9" s="54"/>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+      <c r="N9" s="139" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
       <c r="B10" s="11">
         <v>5</v>
       </c>
-      <c r="C10" s="113"/>
+      <c r="C10" s="117"/>
       <c r="D10" s="15" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="K10" s="60" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="L10" s="60"/>
       <c r="M10" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="N10" s="54"/>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="N10" s="53" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
       <c r="B11" s="11">
         <v>6</v>
       </c>
-      <c r="C11" s="113"/>
+      <c r="C11" s="117"/>
       <c r="D11" s="15" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="G11" s="2">
         <v>12.5</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="K11" s="60" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L11" s="60"/>
       <c r="M11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="N11" s="54"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+      <c r="N11" s="53" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
       <c r="B12" s="7">
         <f t="shared" ref="B12" si="0">B11+1</f>
         <v>7</v>
       </c>
-      <c r="C12" s="113"/>
+      <c r="C12" s="117"/>
       <c r="D12" s="15" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="G12" s="2">
         <v>12.5</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K12" s="60" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="L12" s="60"/>
       <c r="M12" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="N12" s="54"/>
-    </row>
-    <row r="13" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+      <c r="N12" s="53" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" ht="15" customHeight="1">
       <c r="B13" s="11">
         <v>8</v>
       </c>
-      <c r="C13" s="113"/>
+      <c r="C13" s="117"/>
       <c r="D13" s="16" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G13" s="18">
         <v>12.5</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="K13" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="L13" s="105"/>
+        <v>47</v>
+      </c>
+      <c r="K13" s="137" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13" s="137"/>
       <c r="M13" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="N13" s="16"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="N13" s="140" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14">
       <c r="B14" s="11">
         <v>9</v>
       </c>
-      <c r="C14" s="113"/>
+      <c r="C14" s="117"/>
       <c r="D14" s="16" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G14" s="18">
         <v>12.5</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="K14" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="L14" s="105"/>
+        <v>47</v>
+      </c>
+      <c r="K14" s="137" t="s">
+        <v>48</v>
+      </c>
+      <c r="L14" s="137"/>
       <c r="M14" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="N14" s="16"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="N14" s="140" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
       <c r="B15" s="7">
         <v>10</v>
       </c>
-      <c r="C15" s="113"/>
+      <c r="C15" s="117"/>
       <c r="D15" s="16" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>52</v>
+        <v>143</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="G15" s="18">
         <v>12.5</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="K15" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="L15" s="105"/>
+        <v>47</v>
+      </c>
+      <c r="K15" s="137" t="s">
+        <v>48</v>
+      </c>
+      <c r="L15" s="137"/>
       <c r="M15" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="N15" s="16"/>
-    </row>
-    <row r="16" spans="2:14" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="N15" s="141" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" ht="14.1" customHeight="1">
       <c r="B16" s="11">
         <v>11</v>
       </c>
-      <c r="C16" s="113"/>
+      <c r="C16" s="117"/>
       <c r="D16" s="16" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G16" s="18">
         <v>12.5</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="K16" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="L16" s="105"/>
+        <v>47</v>
+      </c>
+      <c r="K16" s="137" t="s">
+        <v>48</v>
+      </c>
+      <c r="L16" s="137"/>
       <c r="M16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="N16" s="54"/>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+      <c r="N16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16">
       <c r="B17" s="11">
         <v>12</v>
       </c>
-      <c r="C17" s="113"/>
+      <c r="C17" s="117"/>
       <c r="D17" s="16" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="G17" s="18">
         <v>-0.01</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="K17" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="L17" s="105"/>
+        <v>47</v>
+      </c>
+      <c r="K17" s="137" t="s">
+        <v>48</v>
+      </c>
+      <c r="L17" s="137"/>
       <c r="M17" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="N17" s="37"/>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="N17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16">
       <c r="B18" s="11">
         <v>13</v>
       </c>
-      <c r="C18" s="113"/>
+      <c r="C18" s="117"/>
       <c r="D18" s="16" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="G18" s="18">
         <v>0.01</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="K18" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="L18" s="105"/>
+        <v>47</v>
+      </c>
+      <c r="K18" s="137" t="s">
+        <v>48</v>
+      </c>
+      <c r="L18" s="137"/>
       <c r="M18" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="N18" s="55"/>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="N18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16">
       <c r="B19" s="11">
         <v>14</v>
       </c>
-      <c r="C19" s="113"/>
+      <c r="C19" s="117"/>
       <c r="D19" s="16" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I19" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="K19" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="L19" s="105"/>
+        <v>47</v>
+      </c>
+      <c r="K19" s="137" t="s">
+        <v>48</v>
+      </c>
+      <c r="L19" s="137"/>
       <c r="M19" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="N19" s="55"/>
-    </row>
-    <row r="20" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="N19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" ht="15" customHeight="1">
       <c r="B20" s="11">
         <v>15</v>
       </c>
-      <c r="C20" s="135"/>
+      <c r="C20" s="118"/>
       <c r="D20" s="16" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I20" s="18" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="K20" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="L20" s="105"/>
+        <v>47</v>
+      </c>
+      <c r="K20" s="137" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="137"/>
       <c r="M20" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="N20" s="7"/>
-    </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="N20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16">
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
       <c r="D21" s="14"/>
@@ -4533,9 +4588,9 @@
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
     </row>
-    <row r="22" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:16" ht="14.45" customHeight="1">
       <c r="B22" s="13" t="s">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="14"/>
@@ -4545,129 +4600,133 @@
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
-      <c r="K22" s="87"/>
-      <c r="L22" s="87"/>
+      <c r="K22" s="69"/>
+      <c r="L22" s="69"/>
       <c r="M22" s="5"/>
     </row>
-    <row r="23" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:16" ht="15.95" thickBot="1">
       <c r="M23" s="5"/>
     </row>
-    <row r="24" spans="2:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="C24" s="123" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="124"/>
-      <c r="E24" s="124"/>
-      <c r="F24" s="125"/>
+    <row r="24" spans="2:16" ht="15.95" thickTop="1">
+      <c r="C24" s="110" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" s="112"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="113"/>
       <c r="G24" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="H24" s="123" t="s">
-        <v>56</v>
-      </c>
-      <c r="I24" s="126"/>
-      <c r="J24" s="124"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="125"/>
-      <c r="M24" s="123" t="s">
-        <v>57</v>
-      </c>
-      <c r="N24" s="126"/>
-      <c r="O24" s="124"/>
-      <c r="P24" s="125"/>
-    </row>
-    <row r="25" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="119" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="120" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="121" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" s="121" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25" s="122" t="s">
-        <v>61</v>
-      </c>
-      <c r="G25" s="131" t="s">
-        <v>62</v>
-      </c>
-      <c r="H25" s="127" t="s">
-        <v>63</v>
-      </c>
-      <c r="I25" s="128"/>
-      <c r="J25" s="121" t="s">
-        <v>58</v>
-      </c>
-      <c r="K25" s="121" t="s">
-        <v>59</v>
-      </c>
-      <c r="L25" s="122" t="s">
-        <v>60</v>
-      </c>
-      <c r="M25" s="132" t="s">
-        <v>63</v>
-      </c>
-      <c r="N25" s="121" t="s">
-        <v>58</v>
-      </c>
-      <c r="O25" s="121" t="s">
-        <v>59</v>
-      </c>
-      <c r="P25" s="122" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B26" s="119"/>
-      <c r="C26" s="120"/>
-      <c r="D26" s="121"/>
-      <c r="E26" s="121"/>
-      <c r="F26" s="122"/>
-      <c r="G26" s="131"/>
-      <c r="H26" s="129"/>
-      <c r="I26" s="130"/>
-      <c r="J26" s="121"/>
-      <c r="K26" s="121"/>
-      <c r="L26" s="122"/>
-      <c r="M26" s="133"/>
-      <c r="N26" s="121"/>
-      <c r="O26" s="121"/>
-      <c r="P26" s="122"/>
-    </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="H24" s="110" t="s">
+        <v>152</v>
+      </c>
+      <c r="I24" s="111"/>
+      <c r="J24" s="112"/>
+      <c r="K24" s="112"/>
+      <c r="L24" s="113"/>
+      <c r="M24" s="110" t="s">
+        <v>153</v>
+      </c>
+      <c r="N24" s="111"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="113"/>
+    </row>
+    <row r="25" spans="2:16" ht="14.45" customHeight="1">
+      <c r="B25" s="124" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="125" t="s">
+        <v>154</v>
+      </c>
+      <c r="D25" s="109" t="s">
+        <v>155</v>
+      </c>
+      <c r="E25" s="109" t="s">
+        <v>156</v>
+      </c>
+      <c r="F25" s="108" t="s">
+        <v>157</v>
+      </c>
+      <c r="G25" s="130" t="s">
+        <v>158</v>
+      </c>
+      <c r="H25" s="126" t="s">
+        <v>159</v>
+      </c>
+      <c r="I25" s="127"/>
+      <c r="J25" s="109" t="s">
+        <v>154</v>
+      </c>
+      <c r="K25" s="109" t="s">
+        <v>155</v>
+      </c>
+      <c r="L25" s="108" t="s">
+        <v>156</v>
+      </c>
+      <c r="M25" s="114" t="s">
+        <v>159</v>
+      </c>
+      <c r="N25" s="109" t="s">
+        <v>154</v>
+      </c>
+      <c r="O25" s="109" t="s">
+        <v>155</v>
+      </c>
+      <c r="P25" s="108" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16">
+      <c r="B26" s="124"/>
+      <c r="C26" s="125"/>
+      <c r="D26" s="109"/>
+      <c r="E26" s="109"/>
+      <c r="F26" s="108"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="128"/>
+      <c r="I26" s="129"/>
+      <c r="J26" s="109"/>
+      <c r="K26" s="109"/>
+      <c r="L26" s="108"/>
+      <c r="M26" s="115"/>
+      <c r="N26" s="109"/>
+      <c r="O26" s="109"/>
+      <c r="P26" s="108"/>
+    </row>
+    <row r="27" spans="2:16">
       <c r="B27" s="24" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="C27" s="20">
+        <v>15</v>
+      </c>
+      <c r="D27" s="22">
         <v>8</v>
       </c>
-      <c r="D27" s="22">
+      <c r="E27" s="22">
+        <v>7</v>
+      </c>
+      <c r="F27" s="23">
         <v>5</v>
       </c>
-      <c r="E27" s="22">
-        <v>3</v>
-      </c>
-      <c r="F27" s="23"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="117" t="s">
-        <v>64</v>
-      </c>
-      <c r="I27" s="118"/>
+      <c r="G27" s="28">
+        <v>5</v>
+      </c>
+      <c r="H27" s="122" t="s">
+        <v>102</v>
+      </c>
+      <c r="I27" s="123"/>
       <c r="J27" s="2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K27" s="22">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L27" s="23">
         <v>0</v>
       </c>
       <c r="M27" s="27" t="s">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="N27" s="2">
         <v>5</v>
@@ -4679,17 +4738,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:16">
       <c r="M28" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="P25:P26"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="K8:L8"/>
     <mergeCell ref="K22:L22"/>
     <mergeCell ref="C6:C20"/>
     <mergeCell ref="B4:B5"/>
@@ -4706,28 +4781,12 @@
     <mergeCell ref="H25:I26"/>
     <mergeCell ref="G25:G26"/>
     <mergeCell ref="K25:K26"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="N25:N26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4745,6 +4804,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="798a38e6de461387c626d04793181ea9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b4b8dab68acb31e3ac71f6347d499c29" ns2:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -4882,43 +4947,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E854E7-906F-4C7C-AFC0-1BC802AE88F0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E854E7-906F-4C7C-AFC0-1BC802AE88F0}"/>
 </file>